--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20232.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -88,21 +88,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>GUERRA</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -112,27 +103,15 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MIXTECO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -142,27 +121,15 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ALEX TADEO</t>
   </si>
   <si>
     <t>MIRANDA</t>
   </si>
   <si>
-    <t>GUADALUPE ANAHI</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
     <t>NAIDELYN</t>
   </si>
   <si>
@@ -175,10 +142,7 @@
     <t>JOSE LUIS</t>
   </si>
   <si>
-    <t>YAEL ISSAI</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
+    <t>EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -631,16 +595,16 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>54.84</v>
+        <v>58.06</v>
       </c>
       <c r="H4">
         <v>6.5</v>
@@ -709,16 +673,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -797,16 +764,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -820,16 +790,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>71.79000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -843,16 +816,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>74.19</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -866,16 +842,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>68.56999999999999</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -889,16 +868,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>58.33</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -912,16 +894,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -935,16 +920,19 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H8">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1009,7 +997,7 @@
         <v>56</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1026,16 +1014,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1049,19 +1037,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>54.84</v>
+        <v>77.42</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1078,16 +1066,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1104,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>45.83</v>
+        <v>58.33</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1127,16 +1115,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1153,16 +1144,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>64.29000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1204,16 +1195,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920261</v>
+        <v>23330051920234</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1233,10 +1224,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1250,22 +1241,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920115</v>
+        <v>23330051920029</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1273,22 +1264,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920155</v>
+        <v>23330051920030</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1296,22 +1287,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920354</v>
+        <v>22330051920007</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1319,16 +1310,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920029</v>
+        <v>23330051920035</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1342,16 +1333,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920030</v>
+        <v>23330051920032</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1360,98 +1351,6 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920007</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920035</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920046</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920141</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20232.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -88,61 +88,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>NAIDELYN</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -696,7 +648,7 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -705,13 +657,13 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -816,16 +768,16 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>74.19</v>
+        <v>77.42</v>
       </c>
       <c r="H4">
         <v>6.5</v>
@@ -917,22 +869,22 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -988,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1014,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>71.79000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1040,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>77.42</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1066,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>68.56999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1092,16 +1044,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>58.33</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1118,16 +1070,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>89.47</v>
+        <v>97.37</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1138,7 +1090,7 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1147,13 +1099,13 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="H8">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1163,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1195,162 +1147,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920234</v>
+        <v>21330051920382</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920107</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920029</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920030</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920007</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920035</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920032</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20232.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -88,10 +88,46 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERSON</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>DIANA PAOLA</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
@@ -1115,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,24 +1183,116 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920382</v>
+        <v>23330051920016</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920025</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920072</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920073</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920382</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G2">
+      <c r="G6">
         <v>2</v>
       </c>
     </row>
